--- a/data/PAREDES AGUILAR ILIANA GABRIELA.xlsx
+++ b/data/PAREDES AGUILAR ILIANA GABRIELA.xlsx
@@ -703,15 +703,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="56" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -728,22 +728,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>febrero</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>marzo</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>abril</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>mayo</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>junio</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>julio</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CONSTRUCCION, INGENIERIA Y TECNOLOGIA CONSTRUINTEC SAS</t>
+          <t>PAREDES AGUILAR ILIANA GABRIELA</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -780,19 +780,46 @@
       </c>
     </row>
     <row r="3">
-      <c r="C3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4" t="n">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PAREDES AGUILAR ILIANA GABRIELA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PAZ ROLDAN BERNABE RAMIRO</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/PAREDES AGUILAR ILIANA GABRIELA.xlsx
+++ b/data/PAREDES AGUILAR ILIANA GABRIELA.xlsx
@@ -439,7 +439,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="56" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
@@ -558,7 +558,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CONSTRUCCION, INGENIERIA Y TECNOLOGIA CONSTRUINTEC SAS</t>
+          <t>PAREDES AGUILAR ILIANA GABRIELA</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">

--- a/data/PAREDES AGUILAR ILIANA GABRIELA.xlsx
+++ b/data/PAREDES AGUILAR ILIANA GABRIELA.xlsx
@@ -708,10 +708,10 @@
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -728,22 +728,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">

--- a/data/PAREDES AGUILAR ILIANA GABRIELA.xlsx
+++ b/data/PAREDES AGUILAR ILIANA GABRIELA.xlsx
@@ -709,8 +709,8 @@
     <col width="33" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
@@ -728,22 +728,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">

--- a/data/PAREDES AGUILAR ILIANA GABRIELA.xlsx
+++ b/data/PAREDES AGUILAR ILIANA GABRIELA.xlsx
@@ -708,10 +708,10 @@
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -728,22 +728,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">

--- a/data/PAREDES AGUILAR ILIANA GABRIELA.xlsx
+++ b/data/PAREDES AGUILAR ILIANA GABRIELA.xlsx
@@ -708,10 +708,10 @@
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -728,22 +728,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
